--- a/automation/reports/Excel/Execution_Summary.xlsx
+++ b/automation/reports/Excel/Execution_Summary.xlsx
@@ -37,7 +37,7 @@
     <t>Pass Percentage</t>
   </si>
   <si>
-    <t>93.9%</t>
+    <t>100%</t>
   </si>
 </sst>
 </file>
@@ -450,7 +450,7 @@
         <v>3</v>
       </c>
       <c r="B4">
-        <v>479</v>
+        <v>510</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
@@ -458,7 +458,7 @@
         <v>4</v>
       </c>
       <c r="B5">
-        <v>26</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
@@ -466,7 +466,7 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
